--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486821_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486821_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.147</v>
+        <v>1.7594</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2671</v>
+        <v>0.1466</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4141</v>
+        <v>1.6128</v>
       </c>
       <c r="G2" t="n">
         <v>1.8697</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5296</v>
+        <v>0.0827</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3864</v>
+        <v>0.0273</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1432</v>
+        <v>0.0554</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5089</v>
+        <v>-0.4701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4119</v>
+        <v>-0.5672</v>
       </c>
       <c r="F3" t="n">
         <v>0.09710000000000001</v>
@@ -688,10 +688,10 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2962</v>
+        <v>0.3172</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5717</v>
+        <v>0.5926</v>
       </c>
       <c r="U3" t="n">
         <v>-0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5114</v>
+        <v>-0.6797</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5958</v>
+        <v>-1.5406</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0845</v>
+        <v>0.861</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2592</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.262</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2211</v>
+        <v>-0.1659</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1274</v>
+        <v>-0.0961</v>
       </c>
       <c r="V4" t="n">
         <v>1.2277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9429</v>
+        <v>-0.8923</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5639</v>
+        <v>-1.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5068</v>
+        <v>0.4677</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2848</v>
+        <v>-0.6404</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1101</v>
+        <v>0.4832</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3949</v>
+        <v>-1.1236</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1228</v>
+        <v>0.2027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>0.9667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>-0.764</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4075</v>
+        <v>-0.8431</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0687</v>
+        <v>-0.4835</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4763</v>
+        <v>-0.3596</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0443</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4411</v>
+        <v>-0.5314</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4854</v>
+        <v>-0.0408</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4004</v>
+        <v>-1.1343</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.36</v>
+        <v>-1.9946</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9596</v>
+        <v>0.8603</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4798</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.059</v>
+        <v>-0.7929</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5798</v>
+        <v>-0.2144</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4792</v>
+        <v>-0.5785</v>
       </c>
       <c r="V6" t="n">
         <v>3.0692</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4398</v>
+        <v>-1.1538</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9323</v>
+        <v>0.2536</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4925</v>
+        <v>-1.4074</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6404</v>
+        <v>-1.2848</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4832</v>
+        <v>0.1101</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1236</v>
+        <v>-1.3949</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2027</v>
+        <v>0.1228</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9667</v>
+        <v>0.0414</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.764</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8431</v>
+        <v>-1.4075</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4835</v>
+        <v>0.0687</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3596</v>
+        <v>-1.4763</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1196</v>
+        <v>-0.2552</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1036</v>
+        <v>0.1308</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.016</v>
+        <v>-0.386</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6125</v>
+        <v>-2.898</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6912</v>
+        <v>-2.0015</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9213</v>
+        <v>-0.8965</v>
       </c>
       <c r="G8" t="n">
         <v>2.2535</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4798</v>
+        <v>-0.7653</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.3933</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3968</v>
+        <v>-0.3719</v>
       </c>
       <c r="V8" t="n">
         <v>-2.4554</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8692</v>
+        <v>-3.6086</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.325</v>
+        <v>-1.0147</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5442</v>
+        <v>-2.5939</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9741</v>
@@ -1156,13 +1156,13 @@
         <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2466</v>
+        <v>-0.986</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6622</v>
+        <v>-0.3519</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5845</v>
+        <v>-0.6341</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8415</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3375</v>
+        <v>-6.1044</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.1185</v>
+        <v>-6.9599</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7811</v>
+        <v>0.8556</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1939</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7228</v>
+        <v>-0.4897</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1927</v>
+        <v>0.3513</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9155</v>
+        <v>-0.841</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.4578</v>
+        <v>-15.1818</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.3141</v>
+        <v>-15.0383</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1433999999999999</v>
+        <v>-0.1433000000000008</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.380500000000001</v>
+        <v>-5.3805</v>
       </c>
       <c r="H11" t="n">
         <v>-4.136900000000001</v>
@@ -1312,16 +1312,16 @@
         <v>9.654</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.9992</v>
+        <v>-3.7233</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8306999999999997</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.1686</v>
+        <v>-3.1684</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2854999999999999</v>
+        <v>-0.2855</v>
       </c>
       <c r="W11" t="n">
         <v>3.8834</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.7628</v>
+        <v>5.3424</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4663</v>
+        <v>3.0184</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2965</v>
+        <v>2.324</v>
       </c>
       <c r="G12" t="n">
         <v>2.7804</v>
@@ -1390,13 +1390,13 @@
         <v>2.3169</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5303</v>
+        <v>2.1099</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8678</v>
+        <v>1.4199</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6625</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8995</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2988</v>
+        <v>4.517</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2694</v>
+        <v>1.3386</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0294</v>
+        <v>3.1784</v>
       </c>
       <c r="G13" t="n">
         <v>1.622</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7541</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7372</v>
+        <v>0.8064</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0169</v>
+        <v>0.1658</v>
       </c>
       <c r="V13" t="n">
         <v>0.5712</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7572</v>
+        <v>3.4635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.2919</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9482</v>
+        <v>3.1717</v>
       </c>
       <c r="G14" t="n">
         <v>0.5326</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6453</v>
+        <v>0.3517</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9099</v>
+        <v>0.3927</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2646</v>
+        <v>-0.0411</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3655</v>
+        <v>2.6994</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0084</v>
+        <v>0.2043</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.643</v>
+        <v>2.4951</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4979</v>
+        <v>-1.4038</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2759</v>
+        <v>-0.8478</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7738</v>
+        <v>-0.5561</v>
       </c>
       <c r="J15" t="n">
-        <v>3.174</v>
+        <v>-1.154</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.433</v>
       </c>
       <c r="L15" t="n">
-        <v>3.174</v>
+        <v>-0.721</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6761</v>
+        <v>-0.2498</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2759</v>
+        <v>-0.4148</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4002</v>
+        <v>0.165</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1324</v>
+        <v>0.9101</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1655</v>
+        <v>0.4822</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0331</v>
+        <v>0.428</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8374</v>
+        <v>2.5185</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6661</v>
+        <v>3.1119</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5035</v>
+        <v>-0.5933</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2358</v>
+        <v>2.4979</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0414</v>
+        <v>-0.2759</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1944</v>
+        <v>2.7738</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2687</v>
+        <v>3.174</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3162</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0476</v>
+        <v>3.174</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0329</v>
+        <v>-0.6761</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2749</v>
+        <v>-0.2759</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.242</v>
+        <v>-0.4002</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3169</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.745</v>
+        <v>0.0206</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2478</v>
+        <v>-0.0621</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4972</v>
+        <v>0.0828</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4142</v>
+        <v>2.051</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8299</v>
+        <v>-1.3558</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2441</v>
+        <v>3.4068</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4038</v>
+        <v>-0.2358</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8478</v>
+        <v>-0.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5561</v>
+        <v>-0.1944</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.154</v>
+        <v>-0.2687</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.433</v>
+        <v>-0.3162</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.721</v>
+        <v>0.0476</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2498</v>
+        <v>0.0329</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4148</v>
+        <v>0.2749</v>
       </c>
       <c r="O17" t="n">
-        <v>0.165</v>
+        <v>-0.242</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
         <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3751</v>
+        <v>0.9585</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5521</v>
+        <v>0.5581</v>
       </c>
       <c r="U17" t="n">
-        <v>0.177</v>
+        <v>0.4005</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8415</v>
+        <v>0.9421</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8415</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2858</v>
+        <v>1.7766</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7982</v>
+        <v>1.2119</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4876</v>
+        <v>0.5647</v>
       </c>
       <c r="G18" t="n">
         <v>1.225</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3254</v>
+        <v>0.1654</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4691</v>
+        <v>-0.0554</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1437</v>
+        <v>0.2208</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6954</v>
+        <v>0.7947</v>
       </c>
       <c r="E19" t="n">
         <v>-0.388</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0834</v>
+        <v>1.1827</v>
       </c>
       <c r="G19" t="n">
         <v>0.5838</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5682</v>
+        <v>-0.4689</v>
       </c>
       <c r="T19" t="n">
         <v>-0.4139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1543</v>
+        <v>-0.0549</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5541</v>
+        <v>-0.8286</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6347</v>
+        <v>-2.221</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0806</v>
+        <v>1.3923</v>
       </c>
       <c r="G20" t="n">
         <v>-0.06320000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.877</v>
+        <v>-0.1516</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2208</v>
+        <v>0.1928</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6562</v>
+        <v>-0.3445</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0924</v>
+        <v>-2.2662</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2797</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8127</v>
+        <v>-0.9865</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4455</v>
@@ -2092,13 +2092,13 @@
         <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>0.16</v>
+        <v>-0.0138</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4359</v>
+        <v>0.2621</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3129</v>
+        <v>-3.2316</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4096</v>
+        <v>-3.7891</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0968</v>
+        <v>0.5575</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7129</v>
@@ -2170,13 +2170,13 @@
         <v>2.1239</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5573</v>
+        <v>0.5239</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4968</v>
+        <v>0.1238</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0606</v>
+        <v>0.4001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2703</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>15.4577</v>
+        <v>16.8367</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1433000000000009</v>
+        <v>0.1434000000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>15.3144</v>
+        <v>16.6934</v>
       </c>
       <c r="G23" t="n">
         <v>5.3805</v>
@@ -2248,16 +2248,16 @@
         <v>15.4461</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9993</v>
+        <v>5.378100000000001</v>
       </c>
       <c r="T23" t="n">
         <v>3.168600000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8306</v>
+        <v>2.2096</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2855999999999999</v>
+        <v>0.2856000000000003</v>
       </c>
       <c r="W23" t="n">
         <v>4.169</v>
